--- a/it_forms/024_tech_startup_data_privacy_audit_form--it_forms.xlsx
+++ b/it_forms/024_tech_startup_data_privacy_audit_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_date</t>
+          <t>form_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Form Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_time</t>
+          <t>form_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Form Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_note</t>
+          <t>form_note_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Form Note 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_integer</t>
+          <t>form_integer_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Form Integer 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_decimal</t>
+          <t>form_decimal_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Form Decimal 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_text</t>
+          <t>form_text_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Form Text 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
